--- a/2025/Protokolle/AWO Sommerfest 2025.xlsx
+++ b/2025/Protokolle/AWO Sommerfest 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubDesktopFiles\AWO\2025\Protokolle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12380238-A0A3-465B-B23C-2B0BAFBB716C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7022ACC4-E6EA-41F0-896F-F5B8506EFEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{214B9ACD-3DA6-4321-AE10-5055D2A92FFB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{214B9ACD-3DA6-4321-AE10-5055D2A92FFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>Sommerfest Spendenbox</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>Bilanz</t>
+  </si>
+  <si>
+    <t>Sommerfest Glasbrenner</t>
+  </si>
+  <si>
+    <t>Sommerfest Bäcker</t>
   </si>
 </sst>
 </file>
@@ -165,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -178,11 +184,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -508,10 +535,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3DB9F7C-83E4-4349-95D8-4B96D8A082DA}">
-  <dimension ref="B4:G15"/>
+  <dimension ref="B4:O21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -602,46 +630,113 @@
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="10">
-        <f>SUM(D11:G12)</f>
-        <v>-310.51</v>
+      <c r="B13" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13" s="15">
+        <v>-324</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="17"/>
+      <c r="E14" s="15">
+        <v>-147.69</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="10">
+        <f>SUM(D10:G14)</f>
+        <v>-834.96</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B17" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="11">
-        <f>D7+D13</f>
-        <v>879.49</v>
-      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="11">
+        <f>D7+D15</f>
+        <v>355.03999999999996</v>
+      </c>
+      <c r="L17" s="12"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="15"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="L18" s="12"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="15"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="L19" s="16"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="15"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="L20" s="16"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="15"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="L21" s="16"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:F5 F6">
-    <cfRule type="cellIs" dxfId="2" priority="2" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5:C6 G5:G6">
-    <cfRule type="cellIs" dxfId="1" priority="3" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="C5:C6 G5:G6 M17:M21">
+    <cfRule type="cellIs" dxfId="5" priority="7" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10:C12">
+    <cfRule type="cellIs" dxfId="4" priority="5" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:F5 F6">
+    <cfRule type="cellIs" dxfId="3" priority="6" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N21">
+    <cfRule type="cellIs" dxfId="2" priority="4" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:C14">
+    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10:C12" xr:uid="{006C8B53-5681-40D4-BFCA-0544DBCD1D31}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C6" xr:uid="{B2184409-B31E-4407-A4B2-E0F086D150F9}">
+      <formula1>$J$1:$J$21</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M17:M21 C10:C14" xr:uid="{006C8B53-5681-40D4-BFCA-0544DBCD1D31}">
       <formula1>$L$1:$L$19</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C6" xr:uid="{B2184409-B31E-4407-A4B2-E0F086D150F9}">
-      <formula1>$J$1:$J$19</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
